--- a/02_DIA_inicio_2026_analisis_assets/rbd_9734_escuela-raul-saez-saez_nt2_nucleos.xlsx
+++ b/02_DIA_inicio_2026_analisis_assets/rbd_9734_escuela-raul-saez-saez_nt2_nucleos.xlsx
@@ -775,13 +775,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C182B31F-2998-470B-B174-648315F6E26D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F1CF1F09-7E8F-43C6-8413-B70596098920}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D6887668-79C6-4E8A-BB23-A2986A17F807}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{713065F0-114D-406E-B914-FF5E469935F5}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{50B2899A-6F68-40D8-B982-29778C67658F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{817900D0-18E4-406E-A3F9-3B6E4322F82F}"/>
 </file>